--- a/PCB/PCBWay-BOM.xlsx
+++ b/PCB/PCBWay-BOM.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -533,2202 +533,2315 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>U_MCU</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>ESP32-S3-WROOM-1-N8R8</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Espressif</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ESP32-S3-WROOM-1-N8R8</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>C2913202</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>verify LCSC/stock</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WiFi/BLE MCU module 8MB+8MB; verify LCSC/stock</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>U_DRV</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>DRV8313PWPR</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Texas Instruments</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>DRV8313PWPR</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>HTSSOP-28</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>C92482</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>thermal pad to GND</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3-phase BLDC gate driver; thermal pad to GND</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>U_BUCK</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>LMR51430YDDCR</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Texas Instruments</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>LMR51430YDDCR</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>SOT-23-6</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>C5210749</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24V-&gt;3.3V 3A buck</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>D_USB</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>USBLC6-2SC6</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>STMicroelectronics</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>USBLC6-2SC6</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>SOT-23-6</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>C7519</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>USB ESD protection array</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Q_WW,Q_CW</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Q_WW;Q_CW</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>AO3400A</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Alpha &amp; Omega</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>AO3400A</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>C20917</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N-MOSFET LED low-side</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Alpha &amp; Omega</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>C15127</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>P-MOSFET reverse-protect</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>D_OR_USB</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>SS14</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>MDD/Diodes</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SS14</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>C2480</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>VBUS diode-OR to buck input</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Schottky 40V 1A; VBUS diode-OR to buck input</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>D_Q1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>BZT52C15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BZT52C10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>BZT52C15</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BZT52C10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>SOD-123</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>C4332</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Q1 Vgs clamp; verify LCSC</t>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C2687029</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Zener 10V 0.5W; Q1 gate-to-source clamp (AO3401A Vgs abs-max +/-12V); verify LCSC</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>TVS1</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>SMBJ30A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SMBJ28A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>SMBJ30A</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMBJ28A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>SMB</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>C13983</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>24V transient clamp</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TVS 28V unidirectional 600W; 24V clamp - small/typical surges below buck 40V abs-max; full-surge VC 45.4V exceeds it (accepted residual risk); verify LCSC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>D_MCU</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>CDSOD323-T03SC</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Bourns</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>ESD 3.3V</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>SOD-323</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>generic 3V3 ESD; optional - may DNP</t>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TVS/ESD 3.3V working; generic 3V3 ESD; optional - may DNP</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>D_CLW,D_CLC</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D_CLW;D_CLC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>clamp</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>SOD-323</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>DNP - populate only if drain ringing &gt;30V</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>LED drain TVS/Schottky; DNP - populate only if drain ringing &gt;30V</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R_AZ_A;R_AZ_B;R_AZ_C</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C25804</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>encoder A/B/Z pull-up stiffening to 3V3; DNP - populate only for a long/noisy encoder cable</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>LED_STATUS</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>19-217/GHC-YR1S2/3T</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Everlight</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Green LED</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>C72043</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>generic green 0603; optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>R_EN,R_BOOT,R_NSLEEP,R_NRESET,R_NFAULT,R_EN_DRV,R_FBB</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>status indicator; generic green 0603; optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>R_EN;R_BOOT;R_NSLEEP;R_NRESET;R_NFAULT;R_EN_DRV;R_FBB</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>0603WAF1002T5E</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>C25804</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>pull-ups + buck FB bottom</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>thick-film 1%; pull-ups + buck FB bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>R_FBT</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>0603WAF4532T5E</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>45.3k</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL 1% - sets Vout=3.318V</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>R_CC1,R_CC2</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>thick-film 1%; CRITICAL 1% - sets Vout=3.318V</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R_CC1;R_CC2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>0603WAF5101T5E</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>5.1k</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>C23186</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>R_DP,R_DM</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>USB-C CC pulldown 1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R_DP;R_DM</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>0603WAF220JT5E</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>22R</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>C25092</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>R_Q1,R_ENB,R_PDW,R_PDC</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>USB series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R_Q1;R_ENB;R_PDW;R_PDC</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>0603WAF1003T5E</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>100k</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>C25803</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>gate pulldowns + buck EN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>R_GW,R_GC</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>thick-film; gate pulldowns + buck EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R_GW;R_GC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>0603WAF330JT5E</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>33R</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>LED gate series</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>R_STATUS</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0603WAF1001T5E</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>UNI-ROYAL</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>C21190</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>C_MCU3,C_MCU4,C_BOOT_B,C_SENS</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>LED series</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C_MCU3;C_MCU4;C_BOOT_B;C_SENS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>100nF</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>C1525</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>decoupling</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X7R 16V; decoupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>C_BOOT</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>CL05C101JB5NNNC</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>100pF</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>GPIO0 debounce - MUST stay small (never ~0.1uF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>C0G 50V; GPIO0 debounce - MUST stay small (never ~0.1uF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>C_FF</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>CL05C220JB5NNNC</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>22pF</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>buck feed-forward (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>C_MCU2,C_EN</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>C0G 50V; buck feed-forward (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C_MCU2;C_EN</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>CL10B105KB8NNNC</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1uF</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>C15849</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X7R 16V</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>C_VBUS</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>CL10A475KO8NNNC</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>4.7uF</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>C19666</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>VBUS bulk</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X5R 16V; VBUS bulk</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>C_CP</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>CL10B103KB8NNNC</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>10nF</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>charge-pump flying cap (VM-rated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>C_VCP,C_VM1,C_VM2</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>50V X7R; charge-pump flying cap (VM-rated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C_VCP;C_VM1;C_VM2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>CL10B104KB8NNNC</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>100nF</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>C1591</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>VCP + VM decoupling</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>50V X7R; VCP + VM decoupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>C_V3P3</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>CL10A474KO8NNNC</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>470nF</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>DRV V3P3 bypass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>16V X7R; DRV V3P3 bypass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>C_MCU1</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>CL21A106KAYNNNE</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>10uF</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>0805</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>C_OUT1,C_OUT2</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X5R 16V</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C_OUT1;C_OUT2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>CL21A226KOQNNNE</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>22uF</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0805</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>C45783</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>buck output</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X5R 10V; buck output</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>C_IN1</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>CL32B106KBJNNNE</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>10uF</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>1210</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>C46653</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>buck input (derated 50V)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>50V X7R; buck input (derated 50V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>C_IN2</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>CL31B475KCHNNNE</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>4.7uF</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>1206</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>buck input</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>50V X7R; buck input</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>C_MCU_BULK</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>T520D477M006ATE025</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Kemet</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>470uF 6.3V</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>7343 (D)</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>*confirm CAP_D land; cures TX brownout</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>C_IN_BULK,C_VM_BULK</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>polymer/tantalum-polymer; *confirm CAP_D land; cures TX brownout</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C_IN_BULK;C_VM_BULK</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>EEE-FK1H101P</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>100uF 50V</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>8x10.5mm</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>*confirm CAP_V land (8mm can)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>aluminium electrolytic SMD; *confirm CAP_V land (8mm can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>SWPA4030S4R7MT</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Sunlord</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>4.7uH</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>4x4mm</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>*confirm IND43 land; or Wurth 74438335047</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>SW_RST,SW_BOOT</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>shielded power inductor &gt;=1.5A; *confirm IND43 land; or Wurth 74438335047</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SW_RST;SW_BOOT</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TS-1187A-B-A-B</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>XKB/various</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>tactile</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>C318884</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>*confirm TACT land</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SMD pushbutton 4-pad; *confirm TACT land</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>0466002.NR</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0454002.MR</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Littelfuse</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>confirm &gt;=63VDC rating for 24V rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NANO2 6.1x2.7mm</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>slow-blow NANO2 fuse; slo-blo; 125V rating satisfies &gt;=63VDC need; verify FUSE_NANO2 land before fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>J_USB</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>TYPE-C-31-M-12</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>HRO</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>USB-C 16P</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>C165948</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>native USB flash/console</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>USB 2.0 receptacle; native USB flash/console</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>J_BTN</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>B2B-XH-A</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>JST</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>JST-XH 2P</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>THT 2.5mm</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>C144395</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>button SW/GND</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>J_KNOB,J_LED</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>header (mate XHP-2); button SW/GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>J_KNOB;J_LED</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>B3B-XH-A</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>JST</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>JST-XH 3P</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>THT 2.5mm</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>C158012</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>knob A/B/GND and LED V+/W/C</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>header (mate XHP-3); knob A/B/GND and LED V+/W/C</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>J_PWR</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>KF301-5.0-2P</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Cixi Kefa</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Screw 2P 5.0mm</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>THT</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>24V V+/V-; verify LCSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>terminal block; 24V V+/V-; verify LCSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>J_MOTOR</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>KF301-5.0-3P</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Cixi Kefa</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Screw 3P 5.0mm</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>THT</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>motor U/V/W; verify LCSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>terminal block; motor U/V/W; verify LCSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>J_SENSOR</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>KF350-3.5-5P</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Cixi Kefa</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Screw 5P 3.5mm</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>THT</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>encoder VCC/GND/A/B/Z; verify LCSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>terminal block; encoder VCC/GND/A/B/Z; verify LCSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>J_EXP</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>(generic 1x10 2.54mm header)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>GPIO header 1x10</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>THT 2.54mm</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>PTH</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>spare IO1/IO2/IO13/IO38-42 + 3V3/GND; DNP if you prefer bare pads</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2.54mm male pin header; spare IO1/IO2/IO13/IO38-42 + 3V3/GND; DNP if you prefer bare pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>J_PROG</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>prog pads</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>SMD pads</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>DNP - bare test pads</t>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>UART fallback pad field; DNP - bare test pads</t>
         </is>
       </c>
     </row>
@@ -2760,13 +2873,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Matches the 68 parts in fusion/BrushlessLamp.sch (authoritative).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+          <t>Matches the 71 parts in fusion/BrushlessLamp.sch (authoritative).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/PCB/PCBWay-BOM.xlsx
+++ b/PCB/PCBWay-BOM.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$K$45</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +30,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -42,12 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,23 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,56 +450,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Item #</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Designator</t>
+          <t>*Designator</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>*Qty</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Manufacturer Part Number</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Manufacturer</t>
+          <t>*Mfg Part #</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Description / Value</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>*Package/Footprint</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -523,12 +513,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Populate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
+          <t>Your Instructions / Notes</t>
         </is>
       </c>
     </row>
@@ -546,14 +531,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Espressif</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ESP32-S3-WROOM-1-N8R8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Espressif</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>ESP32-S3-WROOM-1-N8R8</t>
@@ -571,17 +556,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C2913202</t>
+          <t>C2913201</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>WiFi/BLE MCU module 8MB+8MB; verify LCSC/stock</t>
+          <t>WiFi/BLE MCU module 8MB+8MB; 8MB N8R8 (C2913202 is the N16R8); LCSC verified</t>
         </is>
       </c>
     </row>
@@ -599,14 +579,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>DRV8313PWPR</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>DRV8313PWPR</t>
@@ -628,11 +608,6 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>3-phase BLDC gate driver; thermal pad to GND</t>
         </is>
@@ -652,14 +627,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LMR51430YDDCR</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>LMR51430YDDCR</t>
@@ -681,11 +656,6 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>24V-&gt;3.3V 3A buck</t>
         </is>
@@ -705,14 +675,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>USBLC6-2SC6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>STMicroelectronics</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>USBLC6-2SC6</t>
@@ -734,11 +704,6 @@
         </is>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>USB ESD protection array</t>
         </is>
@@ -758,14 +723,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Alpha &amp; Omega</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>AO3400A</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Alpha &amp; Omega</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>AO3400A</t>
@@ -787,11 +752,6 @@
         </is>
       </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>N-MOSFET LED low-side</t>
         </is>
@@ -811,14 +771,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Alpha &amp; Omega</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Alpha &amp; Omega</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>AO3401A</t>
@@ -840,11 +800,6 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
         <is>
           <t>P-MOSFET reverse-protect</t>
         </is>
@@ -864,14 +819,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MDD/Diodes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SS14</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MDD/Diodes</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>SS14</t>
@@ -893,11 +848,6 @@
         </is>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>Schottky 40V 1A; VBUS diode-OR to buck input</t>
         </is>
@@ -917,14 +867,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Shikues</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>BZT52C10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>various</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>BZT52C10</t>
@@ -942,17 +892,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C2687029</t>
+          <t>C216719</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Zener 10V 0.5W; Q1 gate-to-source clamp (AO3401A Vgs abs-max +/-12V); verify LCSC</t>
+          <t>Zener 10V 0.5W; Q1 gate-to-source clamp (AO3401A Vgs abs-max +/-12V)</t>
         </is>
       </c>
     </row>
@@ -970,14 +915,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Littelfuse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SMBJ28A</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>various</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>SMBJ28A</t>
@@ -993,15 +938,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C178227</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>TVS 28V unidirectional 600W; 24V clamp - small/typical surges below buck 40V abs-max; full-surge VC 45.4V exceeds it (accepted residual risk); verify LCSC</t>
+          <t>TVS 28V unidirectional 600W; 24V clamp - small/typical surges below buck 38V abs-max; full-surge VC 45.4V exceeds it (accepted residual risk)</t>
         </is>
       </c>
     </row>
@@ -1019,14 +963,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Bourns</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CDSOD323-T03SC</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bourns</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>ESD 3.3V</t>
@@ -1042,119 +986,108 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C840638</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>TVS/ESD 3.3V working; generic 3V3 ESD; optional - may DNP</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>D_CLW;D_CLC</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>clamp</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>SOD-323</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>LED drain TVS/Schottky; DNP - populate only if drain ringing &gt;30V</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>R_AZ_A;R_AZ_B;R_AZ_C</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>0603WAF1002T5E</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>SMD</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>C25804</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>encoder A/B/Z pull-up stiffening to 3V3; DNP - populate only for a long/noisy encoder cable</t>
         </is>
@@ -1174,14 +1107,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Everlight</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>19-217/GHC-YR1S2/3T</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Everlight</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Green LED</t>
@@ -1203,11 +1136,6 @@
         </is>
       </c>
       <c r="J14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
         <is>
           <t>status indicator; generic green 0603; optional</t>
         </is>
@@ -1227,14 +1155,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>0603WAF1002T5E</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>10k</t>
@@ -1256,11 +1184,6 @@
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>thick-film 1%; pull-ups + buck FB bottom</t>
         </is>
@@ -1280,14 +1203,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>0603WAF4532T5E</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>45.3k</t>
@@ -1303,13 +1226,12 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>C23058</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>thick-film 1%; CRITICAL 1% - sets Vout=3.318V</t>
         </is>
@@ -1329,14 +1251,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>0603WAF5101T5E</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>5.1k</t>
@@ -1358,11 +1280,6 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>USB-C CC pulldown 1%</t>
         </is>
@@ -1382,14 +1299,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>0603WAF220JT5E</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>22R</t>
@@ -1411,11 +1328,6 @@
         </is>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t>USB series</t>
         </is>
@@ -1435,14 +1347,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>0603WAF1003T5E</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>100k</t>
@@ -1464,11 +1376,6 @@
         </is>
       </c>
       <c r="J19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
         <is>
           <t>thick-film; gate pulldowns + buck EN</t>
         </is>
@@ -1488,14 +1395,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>0603WAF330JT5E</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>33R</t>
@@ -1511,15 +1418,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C23140</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>LED gate series</t>
+          <t>LED gate series; 33R 1%</t>
         </is>
       </c>
     </row>
@@ -1537,14 +1443,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>UNI-ROYAL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>0603WAF1001T5E</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1k</t>
@@ -1566,11 +1472,6 @@
         </is>
       </c>
       <c r="J21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
         <is>
           <t>LED series</t>
         </is>
@@ -1590,14 +1491,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>100nF</t>
@@ -1619,11 +1520,6 @@
         </is>
       </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>X7R 16V; decoupling</t>
         </is>
@@ -1643,14 +1539,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>CL05C101JB5NNNC</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>100pF</t>
@@ -1666,15 +1562,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C26409</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>C0G 50V; GPIO0 debounce - MUST stay small (never ~0.1uF)</t>
+          <t>C0G 50V; GPIO0 debounce - MUST stay small (never ~0.1uF); check stock</t>
         </is>
       </c>
     </row>
@@ -1692,14 +1587,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>CL05C220JB5NNNC</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>22pF</t>
@@ -1715,13 +1610,12 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>C70464</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
         <is>
           <t>C0G 50V; buck feed-forward (optional)</t>
         </is>
@@ -1741,14 +1635,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>CL10B105KB8NNNC</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>1uF</t>
@@ -1770,11 +1664,6 @@
         </is>
       </c>
       <c r="J25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
         <is>
           <t>X7R 16V</t>
         </is>
@@ -1794,14 +1683,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>CL10A475KO8NNNC</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>4.7uF</t>
@@ -1823,11 +1712,6 @@
         </is>
       </c>
       <c r="J26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
         <is>
           <t>X5R 16V; VBUS bulk</t>
         </is>
@@ -1847,14 +1731,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>CL10B103KB8NNNC</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>10nF</t>
@@ -1870,13 +1754,12 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C1589</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
         <is>
           <t>50V X7R; charge-pump flying cap (VM-rated)</t>
         </is>
@@ -1896,14 +1779,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>CL10B104KB8NNNC</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>100nF</t>
@@ -1925,11 +1808,6 @@
         </is>
       </c>
       <c r="J28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
         <is>
           <t>50V X7R; VCP + VM decoupling</t>
         </is>
@@ -1949,12 +1827,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CL10A474KO8NNNC</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>CL10B474KO8NNNC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1972,15 +1850,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C105526</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>16V X7R; DRV V3P3 bypass</t>
+          <t>16V X7R; DRV V3P3 bypass (X7R; was X5R MPN not cataloged)</t>
         </is>
       </c>
     </row>
@@ -1998,14 +1875,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>CL21A106KAYNNNE</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>10uF</t>
@@ -2021,13 +1898,12 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C15850</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
         <is>
           <t>X5R 16V</t>
         </is>
@@ -2047,14 +1923,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>CL21A226KOQNNNE</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>22uF</t>
@@ -2076,11 +1952,6 @@
         </is>
       </c>
       <c r="J31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
         <is>
           <t>X5R 10V; buck output</t>
         </is>
@@ -2100,14 +1971,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>CL32B106KBJNNNE</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>10uF</t>
@@ -2129,11 +2000,6 @@
         </is>
       </c>
       <c r="J32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
         <is>
           <t>50V X7R; buck input (derated 50V)</t>
         </is>
@@ -2153,12 +2019,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CL31B475KCHNNNE</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>CL31B475KBHNNNE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2176,15 +2042,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C51205</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>50V X7R; buck input</t>
+          <t>50V X7R; buck input (BH=50V; CH MPN was a typo)</t>
         </is>
       </c>
     </row>
@@ -2202,14 +2067,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Kemet</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>T520D477M006ATE025</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Kemet</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>470uF 6.3V</t>
@@ -2225,15 +2090,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C156460</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>polymer/tantalum-polymer; *confirm CAP_D land; cures TX brownout</t>
+          <t>polymer/tantalum-polymer; *confirm CAP_D land; cures TX brownout; LCSC stock thin-buy ahead or alt T520D477M006ATE030</t>
         </is>
       </c>
     </row>
@@ -2251,14 +2115,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Panasonic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>EEE-FK1H101P</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Panasonic</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>100uF 50V</t>
@@ -2274,15 +2138,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C178548</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>aluminium electrolytic SMD; *confirm CAP_V land (8mm can)</t>
+          <t>aluminium electrolytic SMD; *confirm CAP_V land (D8x10.2mm can)</t>
         </is>
       </c>
     </row>
@@ -2300,14 +2163,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Sunlord</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>SWPA4030S4R7MT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Sunlord</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>4.7uH</t>
@@ -2323,15 +2186,14 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C57269</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>shielded power inductor &gt;=1.5A; *confirm IND43 land; or Wurth 74438335047</t>
+          <t>shielded power inductor &gt;=1.5A; *confirm IND43 land; Wurth 74438335047 alt is 3x3mm (not land-compatible)</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2211,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>XKB/various</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>TS-1187A-B-A-B</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>XKB/various</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>tactile</t>
@@ -2379,12 +2241,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>SMD pushbutton 4-pad; *confirm TACT land</t>
+          <t>SMD pushbutton 4-pad; XKB TS-1187A-B-A-B land pattern, datasheet-verified; internal contacts bridge pads pairwise per side</t>
         </is>
       </c>
     </row>
@@ -2402,14 +2259,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Littelfuse</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>0454002.MR</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Littelfuse</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>2A</t>
@@ -2425,13 +2282,12 @@
           <t>SMD</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C179005</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
         <is>
           <t>slow-blow NANO2 fuse; slo-blo; 125V rating satisfies &gt;=63VDC need; verify FUSE_NANO2 land before fab</t>
         </is>
@@ -2451,14 +2307,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>TYPE-C-31-M-12</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>HRO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>USB-C 16P</t>
@@ -2481,12 +2337,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>USB 2.0 receptacle; native USB flash/console</t>
+          <t>USB-C receptacle; shell legs require PLATED SLOTS: 4x 0.6x1.7mm. Drill file represents each slot as overlapping 0.6mm drills - cut as slots per the Milling layer, do NOT drill as round holes (previous order T-1P9W1088173A failed on this).</t>
         </is>
       </c>
     </row>
@@ -2504,14 +2355,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>B2B-XH-A</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>JST-XH 2P</t>
@@ -2524,7 +2375,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PTH</t>
+          <t>THT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2533,11 +2384,6 @@
         </is>
       </c>
       <c r="J40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
         <is>
           <t>header (mate XHP-2); button SW/GND</t>
         </is>
@@ -2557,14 +2403,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>B3B-XH-A</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>JST-XH 3P</t>
@@ -2577,7 +2423,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PTH</t>
+          <t>THT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2586,11 +2432,6 @@
         </is>
       </c>
       <c r="J41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
         <is>
           <t>header (mate XHP-3); knob A/B/GND and LED V+/W/C</t>
         </is>
@@ -2610,14 +2451,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Cixi Kefa</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>KF301-5.0-2P</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Cixi Kefa</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Screw 2P 5.0mm</t>
@@ -2630,18 +2471,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PTH</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C474881</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>terminal block; 24V V+/V-; verify LCSC</t>
+          <t>terminal block; 24V V+/V-</t>
         </is>
       </c>
     </row>
@@ -2659,14 +2499,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Cixi Kefa</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>KF301-5.0-3P</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Cixi Kefa</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Screw 3P 5.0mm</t>
@@ -2679,18 +2519,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PTH</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C474882</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>terminal block; motor U/V/W; verify LCSC</t>
+          <t>terminal block; motor U/V/W</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2539,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>J_SENSOR</t>
+          <t>J_SENSOR-A</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2708,17 +2547,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KF350-3.5-5P</t>
+          <t>Cixi Kefa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cixi Kefa</t>
+          <t>KF350-3.5-3P</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Screw 5P 3.5mm</t>
+          <t>Screw 3P 3.5mm</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2728,18 +2567,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PTH</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C474893</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>terminal block; encoder VCC/GND/A/B/Z; verify LCSC</t>
+          <t>terminal block; encoder VCC/GND/A - 3P half; gangs with J_SENSOR-B onto the 5-pos 3.5mm SCREW5 footprint (no 5P block stocked on LCSC). Both BOM lines mount at CPL designator J_SENSOR.</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2587,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>J_EXP</t>
+          <t>J_SENSOR-B</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2757,38 +2595,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(generic 1x10 2.54mm header)</t>
+          <t>Cixi Kefa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>KF350-3.5-2P</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GPIO header 1x10</t>
+          <t>Screw 2P 3.5mm</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>THT 2.54mm</t>
+          <t>THT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PTH</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C474892</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2.54mm male pin header; spare IO1/IO2/IO13/IO38-42 + 3V3/GND; DNP if you prefer bare pads</t>
+          <t>terminal block; encoder B/Z - 2P half; butts against J_SENSOR-A to fill the 5-pos block. Mounts at CPL designator J_SENSOR (see J_SENSOR-A).</t>
         </is>
       </c>
     </row>
@@ -2798,55 +2635,97 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>J_EXP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BOOMELE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2.54-1*10P</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GPIO header 1x10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>THT 2.54mm</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C57369</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2.54mm male pin header; spare IO1/IO2/IO13/IO38-42 + 3V3/GND; DNP if you prefer bare pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>J_PROG</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>prog pads</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>SMD pads</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>UART fallback pad field; DNP - bare test pads</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2857,73 +2736,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>BrushlessLamp custom PCB — PCBWay assembly BOM</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>PCBWay order remarks (paste into the order notes field):</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Matches the 71 parts in fusion/BrushlessLamp.sch (authoritative).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>USB-C (J_USB) shell legs are PLATED SLOTS: 4x 0.6x1.7mm. The drill file shows them as overlapping 0.6mm drills; follow the slots / Milling layer, do not drill round holes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BOM lines J_SENSOR-A (KF350-3.5-3P) and J_SENSOR-B (KF350-3.5-2P) are gangable halves that together populate the single 5-position footprint at CPL designator J_SENSOR.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Populate column: 'DNP' rows (highlighted) = do NOT place (bare pads).</t>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DNS lines (D_CLW, D_CLC, R_AZ_A/B/C, J_PROG) are do-not-populate.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Type: SMD = surface-mount, PTH = plated through-hole (the 7 connectors).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Passives without an MPN: source by Value+Package+tolerance (equivalents OK).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Exact MPN required for: ESP32-S3-WROOM-1-N8R8, DRV8313PWPR, LMR51430YDDCR,</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  USBLC6-2SC6, AO3400A, TYPE-C-31-M-12, the JST-XH and KF screw terminals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4 part-specific parts (confirm footprint vs chosen part): C_MCU_BULK (470uF polymer),</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C_IN_BULK/C_VM_BULK (100uF 50V elec), L1 (4.7uH inductor), SW_RST/SW_BOOT (tactile).</t>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Board is 55x55mm, 4-layer; inner planes L2=GND, L15=3V3.</t>
         </is>
       </c>
     </row>
